--- a/Roma_2027.xlsx
+++ b/Roma_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE2990AF-43C1-4FB7-9B30-0C8E7F4AF455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE003391-B5C4-4ACE-91B0-D4AE11706815}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{370BB6BA-2F30-4775-942F-04016D8D18C4}"/>
   </bookViews>
@@ -5699,9 +5699,6 @@
     <t>Cesano</t>
   </si>
   <si>
-    <t>Via di Monte Polacco, 2</t>
-  </si>
-  <si>
     <t>Via Giovanni da Castel Bolognese, 63</t>
   </si>
   <si>
@@ -5717,9 +5714,6 @@
     <t>Via dei Basaldella</t>
   </si>
   <si>
-    <t>Via Flaminia Vecchia, 732</t>
-  </si>
-  <si>
     <t>Viale delle Provincie, 30</t>
   </si>
   <si>
@@ -5727,6 +5721,12 @@
   </si>
   <si>
     <t>Via Tor de' Schiavi, 295</t>
+  </si>
+  <si>
+    <t>Via Flaminia, 732</t>
+  </si>
+  <si>
+    <t>Via di Monte Polacco, 4</t>
   </si>
 </sst>
 </file>
@@ -11011,7 +11011,7 @@
         <v>177</v>
       </c>
       <c r="F45" s="68" t="s">
-        <v>1886</v>
+        <v>1895</v>
       </c>
       <c r="G45" s="48" t="s">
         <v>202</v>
@@ -26283,7 +26283,7 @@
         <v>168</v>
       </c>
       <c r="F184" s="39" t="s">
-        <v>1887</v>
+        <v>1886</v>
       </c>
       <c r="G184" s="35" t="s">
         <v>199</v>
@@ -28501,7 +28501,7 @@
         <v>167</v>
       </c>
       <c r="F204" s="39" t="s">
-        <v>1888</v>
+        <v>1887</v>
       </c>
       <c r="G204" s="35" t="s">
         <v>242</v>
@@ -40407,7 +40407,7 @@
         <v>159</v>
       </c>
       <c r="F312" s="68" t="s">
-        <v>1889</v>
+        <v>1888</v>
       </c>
       <c r="G312" s="48" t="s">
         <v>211</v>
@@ -44501,7 +44501,7 @@
         <v>35</v>
       </c>
       <c r="F349" s="68" t="s">
-        <v>1890</v>
+        <v>1889</v>
       </c>
       <c r="G349" s="48" t="s">
         <v>224</v>
@@ -48691,7 +48691,7 @@
         <v>28</v>
       </c>
       <c r="F387" s="20" t="s">
-        <v>1891</v>
+        <v>1890</v>
       </c>
       <c r="G387" s="16" t="s">
         <v>258</v>
@@ -49343,7 +49343,7 @@
         <v>1167</v>
       </c>
       <c r="F393" s="39" t="s">
-        <v>1892</v>
+        <v>1894</v>
       </c>
       <c r="G393" s="35" t="s">
         <v>634</v>
@@ -51115,7 +51115,7 @@
         <v>28</v>
       </c>
       <c r="F409" s="68" t="s">
-        <v>1893</v>
+        <v>1891</v>
       </c>
       <c r="G409" s="48" t="s">
         <v>237</v>
@@ -51657,7 +51657,7 @@
         <v>28</v>
       </c>
       <c r="F414" s="68" t="s">
-        <v>1894</v>
+        <v>1892</v>
       </c>
       <c r="G414" s="48" t="s">
         <v>562</v>
@@ -51767,7 +51767,7 @@
         <v>28</v>
       </c>
       <c r="F415" s="68" t="s">
-        <v>1895</v>
+        <v>1893</v>
       </c>
       <c r="G415" s="48" t="s">
         <v>560</v>

--- a/Roma_2027.xlsx
+++ b/Roma_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41075A34-69E0-474C-82BE-27188CE94C75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D60E0CC-A2DC-4F18-8DC9-4B67EDE49B85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{370BB6BA-2F30-4775-942F-04016D8D18C4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4420" uniqueCount="1922">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4422" uniqueCount="1924">
   <si>
     <t>Recensore</t>
   </si>
@@ -5805,6 +5805,12 @@
   </si>
   <si>
     <t>41.51116783711071, 12.741851017737611</t>
+  </si>
+  <si>
+    <t>41.8944379009184, 12.493778041993513</t>
+  </si>
+  <si>
+    <t>41.94435489991688, 12.469034833268445</t>
   </si>
 </sst>
 </file>
@@ -6083,7 +6089,7 @@
     <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="71">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -6288,9 +6294,6 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="9" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -6768,7 +6771,7 @@
         <f>+H3+H4</f>
         <v>257</v>
       </c>
-      <c r="I5" s="69"/>
+      <c r="I5" s="9"/>
       <c r="J5" s="9"/>
       <c r="K5" s="9"/>
       <c r="L5" s="9"/>
@@ -11149,7 +11152,9 @@
       <c r="H45" s="48" t="s">
         <v>357</v>
       </c>
-      <c r="I45" s="48"/>
+      <c r="I45" s="68" t="s">
+        <v>1922</v>
+      </c>
       <c r="J45" s="47" t="s">
         <v>491</v>
       </c>
@@ -28485,7 +28490,9 @@
       <c r="H201" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="I201" s="35"/>
+      <c r="I201" s="39" t="s">
+        <v>1923</v>
+      </c>
       <c r="J201" s="34" t="s">
         <v>1202</v>
       </c>
@@ -46872,7 +46879,7 @@
       <c r="H366" s="61" t="s">
         <v>357</v>
       </c>
-      <c r="I366" s="70" t="s">
+      <c r="I366" s="69" t="s">
         <v>1915</v>
       </c>
       <c r="J366" s="60" t="s">

--- a/Roma_2027.xlsx
+++ b/Roma_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E27AED4A-AF6C-4BDF-9A7F-F84F14C78373}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05D5EC9-2EEC-441D-AFD6-5FF561E5AF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{370BB6BA-2F30-4775-942F-04016D8D18C4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4426" uniqueCount="1928">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4432" uniqueCount="1934">
   <si>
     <t>Recensore</t>
   </si>
@@ -5823,6 +5823,24 @@
   </si>
   <si>
     <t>41.89776107504589, 12.468759116941461</t>
+  </si>
+  <si>
+    <t>41.37728946359321, 13.737764537660487</t>
+  </si>
+  <si>
+    <t>41.82955701496672, 13.166111144621077</t>
+  </si>
+  <si>
+    <t>41.82857927673047, 13.143353525815082</t>
+  </si>
+  <si>
+    <t>41.80976549234967, 13.122920514770096</t>
+  </si>
+  <si>
+    <t>41.89472309055656, 12.474234812461015</t>
+  </si>
+  <si>
+    <t>41.89456883018618, 12.474274381610769</t>
   </si>
 </sst>
 </file>
@@ -15509,7 +15527,9 @@
         <v>698</v>
       </c>
       <c r="N84" s="17"/>
-      <c r="Q84" s="16"/>
+      <c r="Q84" s="20" t="s">
+        <v>1929</v>
+      </c>
       <c r="S84" s="1">
         <f t="shared" si="35"/>
         <v>0</v>
@@ -16508,7 +16528,9 @@
         <v>39</v>
       </c>
       <c r="N93" s="17"/>
-      <c r="Q93" s="16"/>
+      <c r="Q93" s="20" t="s">
+        <v>1931</v>
+      </c>
       <c r="S93" s="1">
         <f t="shared" si="47"/>
         <v>0</v>
@@ -22298,7 +22320,9 @@
       <c r="P145" s="38">
         <v>1</v>
       </c>
-      <c r="Q145" s="35"/>
+      <c r="Q145" s="35" t="s">
+        <v>1928</v>
+      </c>
       <c r="S145" s="1">
         <f t="shared" si="63"/>
         <v>0</v>
@@ -27299,7 +27323,9 @@
         <v>698</v>
       </c>
       <c r="N190" s="17"/>
-      <c r="Q190" s="16"/>
+      <c r="Q190" s="20" t="s">
+        <v>1930</v>
+      </c>
       <c r="S190" s="1">
         <f t="shared" si="63"/>
         <v>0</v>
@@ -48249,7 +48275,9 @@
       </c>
       <c r="O378" s="51"/>
       <c r="P378" s="51"/>
-      <c r="Q378" s="48"/>
+      <c r="Q378" s="48" t="s">
+        <v>1933</v>
+      </c>
       <c r="S378" s="1">
         <f t="shared" si="111"/>
         <v>1</v>
@@ -50582,7 +50610,9 @@
       </c>
       <c r="O399" s="51"/>
       <c r="P399" s="51"/>
-      <c r="Q399" s="48"/>
+      <c r="Q399" s="48" t="s">
+        <v>1932</v>
+      </c>
       <c r="S399" s="1">
         <f t="shared" si="139"/>
         <v>1</v>

--- a/Roma_2027.xlsx
+++ b/Roma_2027.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\scarg\Dropbox\PNE Simone\Guide\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D05D5EC9-2EEC-441D-AFD6-5FF561E5AF6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29A1FB2-5F2B-41A4-8245-7AA24C818C45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="665" xr2:uid="{370BB6BA-2F30-4775-942F-04016D8D18C4}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4432" uniqueCount="1934">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4432" uniqueCount="1936">
   <si>
     <t>Recensore</t>
   </si>
@@ -5841,6 +5841,12 @@
   </si>
   <si>
     <t>41.89456883018618, 12.474274381610769</t>
+  </si>
+  <si>
+    <t>Luca Veglianti (chiuso)</t>
+  </si>
+  <si>
+    <t>41.768741212395845, 12.661723908109279</t>
   </si>
 </sst>
 </file>
@@ -6751,15 +6757,15 @@
       </c>
       <c r="F4" s="7">
         <f>+AE6</f>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G4" s="7">
         <f>+AG6</f>
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="H4" s="5">
         <f>+E4-G4</f>
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="I4" s="22" t="s">
         <v>10</v>
@@ -6783,15 +6789,15 @@
       </c>
       <c r="F5" s="8">
         <f>+F3+F4</f>
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="G5" s="8">
         <f>+G3+G4</f>
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H5" s="8">
         <f>+H3+H4</f>
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I5" s="33" t="s">
         <v>16</v>
@@ -6892,7 +6898,7 @@
       </c>
       <c r="AE6" s="1">
         <f t="shared" si="1"/>
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="AF6" s="1">
         <f t="shared" si="1"/>
@@ -6900,7 +6906,7 @@
       </c>
       <c r="AG6" s="1">
         <f t="shared" si="1"/>
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AH6" s="1">
         <f t="shared" si="1"/>
@@ -10060,11 +10066,9 @@
       <c r="F35" s="42" t="s">
         <v>1478</v>
       </c>
-      <c r="G35" s="42" t="s">
+      <c r="G35" s="42"/>
+      <c r="H35" s="42" t="s">
         <v>1148</v>
-      </c>
-      <c r="H35" s="42" t="s">
-        <v>357</v>
       </c>
       <c r="I35" s="41" t="s">
         <v>1480</v>
@@ -10082,7 +10086,9 @@
       <c r="P35" s="46">
         <v>1</v>
       </c>
-      <c r="Q35" s="42"/>
+      <c r="Q35" s="57" t="s">
+        <v>1935</v>
+      </c>
       <c r="S35" s="1">
         <f t="shared" si="7"/>
         <v>0</v>
@@ -17822,51 +17828,53 @@
       </c>
     </row>
     <row r="105" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="47">
-        <v>0</v>
-      </c>
-      <c r="B105" s="47">
-        <v>1</v>
-      </c>
-      <c r="C105" s="47">
+      <c r="A105" s="34">
+        <v>0</v>
+      </c>
+      <c r="B105" s="34">
+        <v>1</v>
+      </c>
+      <c r="C105" s="34">
         <v>3</v>
       </c>
-      <c r="D105" s="48" t="s">
+      <c r="D105" s="35" t="s">
         <v>142</v>
       </c>
-      <c r="E105" s="48" t="s">
+      <c r="E105" s="35" t="s">
         <v>177</v>
       </c>
-      <c r="F105" s="48" t="s">
+      <c r="F105" s="35" t="s">
         <v>345</v>
       </c>
-      <c r="G105" s="48" t="s">
+      <c r="G105" s="35" t="s">
         <v>39</v>
       </c>
-      <c r="H105" s="48" t="s">
+      <c r="H105" s="35" t="s">
         <v>379</v>
       </c>
-      <c r="I105" s="47" t="s">
+      <c r="I105" s="34" t="s">
         <v>493</v>
       </c>
-      <c r="J105" s="47">
+      <c r="J105" s="34">
         <v>16</v>
       </c>
-      <c r="K105" s="49" t="s">
+      <c r="K105" s="36" t="s">
         <v>709</v>
       </c>
-      <c r="L105" s="49" t="s">
+      <c r="L105" s="36" t="s">
         <v>694</v>
       </c>
-      <c r="M105" s="50" t="s">
+      <c r="M105" s="37" t="s">
         <v>1407</v>
       </c>
-      <c r="N105" s="50" t="s">
-        <v>1754</v>
-      </c>
-      <c r="O105" s="51"/>
-      <c r="P105" s="51"/>
-      <c r="Q105" s="48"/>
+      <c r="N105" s="37" t="s">
+        <v>1763</v>
+      </c>
+      <c r="O105" s="38">
+        <v>1</v>
+      </c>
+      <c r="P105" s="38"/>
+      <c r="Q105" s="35"/>
       <c r="S105" s="1">
         <f t="shared" si="35"/>
         <v>0</v>
@@ -17913,7 +17921,7 @@
       </c>
       <c r="AE105" s="1">
         <f t="shared" si="46"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF105" s="1">
         <f t="shared" si="19"/>
@@ -17921,7 +17929,7 @@
       </c>
       <c r="AG105" s="1">
         <f t="shared" si="20"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH105" s="1">
         <f t="shared" si="21"/>
@@ -39317,53 +39325,53 @@
       </c>
     </row>
     <row r="298" spans="1:35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A298" s="52">
-        <v>0</v>
-      </c>
-      <c r="B298" s="52">
+      <c r="A298" s="34">
+        <v>0</v>
+      </c>
+      <c r="B298" s="34">
         <v>2</v>
       </c>
-      <c r="C298" s="52">
-        <v>1</v>
-      </c>
-      <c r="D298" s="53" t="s">
+      <c r="C298" s="34">
+        <v>1</v>
+      </c>
+      <c r="D298" s="35" t="s">
         <v>1332</v>
       </c>
-      <c r="E298" s="53" t="s">
+      <c r="E298" s="35" t="s">
         <v>1352</v>
       </c>
-      <c r="F298" s="53" t="s">
+      <c r="F298" s="35" t="s">
         <v>1315</v>
       </c>
-      <c r="G298" s="53" t="s">
+      <c r="G298" s="35" t="s">
         <v>1316</v>
       </c>
-      <c r="H298" s="53" t="s">
+      <c r="H298" s="35" t="s">
         <v>357</v>
       </c>
-      <c r="I298" s="52" t="s">
+      <c r="I298" s="34" t="s">
         <v>1317</v>
       </c>
-      <c r="J298" s="52">
+      <c r="J298" s="34">
         <v>99</v>
       </c>
-      <c r="K298" s="54" t="s">
+      <c r="K298" s="36" t="s">
         <v>962</v>
       </c>
-      <c r="L298" s="54" t="s">
+      <c r="L298" s="36" t="s">
         <v>720</v>
       </c>
-      <c r="M298" s="55" t="s">
+      <c r="M298" s="37" t="s">
         <v>721</v>
       </c>
-      <c r="N298" s="55" t="s">
-        <v>1763</v>
-      </c>
-      <c r="O298" s="56">
-        <v>1</v>
-      </c>
-      <c r="P298" s="56"/>
-      <c r="Q298" s="53"/>
+      <c r="N298" s="37" t="s">
+        <v>1934</v>
+      </c>
+      <c r="O298" s="38">
+        <v>1</v>
+      </c>
+      <c r="P298" s="38"/>
+      <c r="Q298" s="35"/>
       <c r="S298" s="1">
         <f t="shared" si="95"/>
         <v>0</v>
